--- a/files/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸.xlsx
@@ -35246,10 +35246,47 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>30/F</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>C | 587呎 (2房)
+$960万
+$16,350/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$803万
+$23,131/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$444万
+$16,380/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>30&amp;31/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>A | 1887呎 (4+房)
 暂无价格
@@ -35257,7 +35294,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>B | 2136呎 (4+房)
 暂无价格
@@ -35265,50 +35302,13 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 587呎 (2房)
-$960万
-$16,350/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="D8" s="17" t="inlineStr"/>
       <c r="E8" s="17" t="inlineStr"/>
       <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="17" t="inlineStr"/>
       <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 347呎 (1房)
-$803万
-$23,131/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 271呎 (开放式)
-$444万
-$16,380/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="I8" s="17" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -37278,16 +37278,90 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>30/F</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1,738万
+$21,784/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1,286万
+$25,125/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$858万
+$17,067/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$876万
+$17,619/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$951万
+$17,716/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>F | 516呎 (2房)
+$980万
+$19,001/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$808万
+$23,080/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$963万
+$21,160/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>30&amp;31/F</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>G | 2117呎 (4+房)
 暂无价格
@@ -37295,84 +37369,10 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="17" t="inlineStr"/>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 798呎 (3房)
-$1,738万
-$21,784/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 512呎 (2房)
-$1,286万
-$25,125/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 503呎 (2房)
-$858万
-$17,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-$876万
-$17,619/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$951万
-$17,716/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 516呎 (2房)
-$980万
-$19,001/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr"/>
       <c r="I8" s="17" t="inlineStr"/>
       <c r="J8" s="17" t="inlineStr"/>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 350呎 (1房)
-$808万
-$23,080/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>L | 455呎 (2房)
-$963万
-$21,160/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">

--- a/files/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +151,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +232,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -32629,4 +32820,6799 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2034呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 852呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1670呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 1672呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 852呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1706万
+$20,218/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+$3400万
+$27,157/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1674万
+$19,810/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+$3040万
+$23,787/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1661万
+$19,964/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1579万
+$18,690/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1623万
+$19,230/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$3127万
+$26,038/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1537万
+$18,468/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$2050万
+$24,260/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+$1568万
+$18,339/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1606万
+$19,023/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1581万
+$19,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1676万
+$19,839/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1590万
+$18,835/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1598万
+$19,202/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1906万
+$22,562/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1590万
+$18,839/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+$3158万
+$24,710/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$3000万
+$24,980/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1510万
+$18,149/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1637万
+$19,375/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+$1662万
+$19,440/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1550万
+$18,365/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1595万
+$19,171/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1513万
+$17,905/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1541万
+$18,522/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1511万
+$17,881/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+$3080万
+$24,100/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+$3600万
+$28,754/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1564万
+$18,800/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1616万
+$19,128/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+$1533万
+$17,925/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$2041万
+$24,187/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1469万
+$17,654/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1600万
+$18,936/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1557万
+$18,448/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+$2720万
+$21,283/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$2568万
+$21,382/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1428万
+$17,163/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1552万
+$18,367/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$2795万
+$23,272/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1389万
+$16,697/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1407万
+$16,648/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+$2945万
+$23,046/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$2695万
+$22,442/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1359万
+$16,334/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1376万
+$16,286/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+$2857万
+$22,354/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$2588万
+$21,549/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1332万
+$16,007/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1349万
+$15,960/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1480万
+$17,788/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1514万
+$17,915/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+$1558万
+$18,461/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1201呎 (4+房)
+$2410万
+$20,068/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1305万
+$15,688/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1780万
+$21,065/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 1329呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 832呎 (3房)
+$1400万
+$16,827/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 845呎 (3房)
+$1309万
+$15,486/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 855呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 844呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 1272呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1212呎 (4+房)
+$3530万
+$29,125/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 806呎 (3房)
+$1800万
+$22,333/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 801呎 (3房)
+$1525万
+$19,039/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 809呎 (3房)
+$1469万
+$18,162/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 816呎 (3房)
+$1645万
+$20,159/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1932呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 753呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1199万
+$17,606/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$2103万
+$30,884/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$2060万
+$30,246/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$2082万
+$30,579/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$2062万
+$30,276/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+$2434万
+$22,727/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$2019万
+$29,650/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1260万
+$18,530/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1138万
+$16,711/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1170万
+$17,211/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1170万
+$17,211/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+$2442万
+$22,802/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1960万
+$28,781/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$1982万
+$29,098/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$2050万
+$19,395/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+$2476万
+$23,116/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1146万
+$16,853/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$2080万
+$19,678/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+$2430万
+$22,689/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1233万
+$18,134/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$2011万
+$19,024/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+$2419万
+$22,590/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1902万
+$27,934/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$1603万
+$23,532/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$2022万
+$19,130/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1883万
+$27,658/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$1493万
+$21,929/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$1995万
+$18,874/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$1479万
+$21,712/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$1970万
+$18,638/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1086万
+$15,967/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$1972万
+$18,657/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1088万
+$15,973/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1086万
+$15,967/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+$2094万
+$19,547/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1100万
+$16,148/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+$2277万
+$27,139/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1076万
+$15,821/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$1922万
+$18,184/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$1050万
+$15,419/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+$1768万
+$21,073/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 681呎 (3房)
+$1194万
+$17,538/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+$2093万
+$19,801/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$946万
+$13,888/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+$2232万
+$26,605/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1043万
+$15,336/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1057呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 1071呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 681呎 (3房)
+$946万
+$13,888/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 839呎 (3房)
+$2210万
+$26,341/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 680呎 (3房)
+$1032万
+$15,183/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1025呎 (4+房)
+$2889万
+$28,183/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1021呎 (3房)
+$2481万
+$24,300/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 660呎 (3房)
+$1088万
+$16,485/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>D | 814呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 651呎 (3房)
+$1478万
+$22,704/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 587呎 (2房)
+$962万
+$16,384/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$583万
+$16,803/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$400万
+$14,769/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 587呎 (2房)
+$960万
+$16,350/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$803万
+$23,131/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$444万
+$16,380/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1887呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2136呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$1084万
+$23,565/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$747万
+$22,046/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$885万
+$17,089/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$771万
+$24,257/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1029万
+$20,499/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$749万
+$21,598/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$647万
+$23,876/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$816万
+$16,058/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$1070万
+$23,266/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$769万
+$22,694/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+$876万
+$16,950/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$756万
+$23,781/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1059万
+$21,102/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$771万
+$22,233/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$408万
+$15,042/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$812万
+$15,978/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$811万
+$17,627/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$754万
+$22,249/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+$866万
+$16,750/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$790万
+$24,842/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 503呎 (2房)
+$1014万
+$20,155/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$756万
+$21,797/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$592万
+$21,856/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$808万
+$15,899/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$726万
+$15,786/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$747万
+$22,029/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$874万
+$16,869/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$532万
+$16,735/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$979万
+$19,508/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$572万
+$16,471/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$451万
+$16,632/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$804万
+$15,819/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$982万
+$21,350/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$739万
+$21,811/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+$882万
+$17,057/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$530万
+$16,679/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 503呎 (2房)
+$970万
+$19,276/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$581万
+$16,756/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$610万
+$22,496/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$888万
+$17,490/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$998万
+$21,703/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$732万
+$21,595/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+$881万
+$17,031/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$530万
+$16,663/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 503呎 (2房)
+$998万
+$19,840/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$699万
+$20,148/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$611万
+$22,539/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$796万
+$15,662/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$988万
+$21,488/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$725万
+$21,381/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$862万
+$16,641/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$759万
+$23,872/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$835万
+$16,633/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$727万
+$20,946/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$598万
+$22,053/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1114万
+$21,923/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$949万
+$20,640/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$718万
+$21,169/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$857万
+$16,550/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$524万
+$16,482/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$981万
+$19,540/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$720万
+$20,739/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$592万
+$21,835/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1077万
+$21,207/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$940万
+$20,436/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$711万
+$20,960/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+$1277万
+$24,700/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$744万
+$23,402/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$925万
+$18,425/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$713万
+$20,534/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$585万
+$21,582/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1009万
+$19,860/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$989万
+$21,498/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (1房)
+$704万
+$20,752/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+$1212万
+$23,450/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$529万
+$16,648/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$962万
+$19,155/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$672万
+$19,362/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$552万
+$20,351/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1009万
+$19,860/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$989万
+$21,498/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$697万
+$20,752/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$596万
+$19,720/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$595万
+$22,352/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$692万
+$21,746/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$962万
+$19,155/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$705万
+$20,330/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$552万
+$20,351/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$990万
+$19,489/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$970万
+$21,076/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$675万
+$20,103/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$584万
+$19,333/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$619万
+$23,283/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$697万
+$21,930/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$931万
+$18,537/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$683万
+$19,690/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$568万
+$20,949/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$980万
+$19,296/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$903万
+$19,640/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$669万
+$19,904/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$578万
+$19,142/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$613万
+$23,053/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$690万
+$21,713/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$921万
+$18,354/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$509万
+$14,670/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$535万
+$19,754/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$768万
+$15,125/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$768万
+$16,696/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$662万
+$19,707/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$601万
+$19,900/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$416万
+$15,650/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$529万
+$16,633/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$912万
+$18,172/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$670万
+$19,302/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$530万
+$19,559/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$961万
+$18,916/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$690万
+$15,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$656万
+$19,512/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 301呎 (1房)
+$595万
+$19,768/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$595万
+$22,375/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$637万
+$20,033/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$903万
+$17,992/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$663万
+$19,111/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$551万
+$20,333/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$761万
+$14,974/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$775万
+$16,857/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$618万
+$18,399/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$589万
+$19,508/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$560万
+$21,059/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$631万
+$19,835/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$894万
+$17,814/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$657万
+$18,921/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$559万
+$20,611/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$897万
+$17,660/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$922万
+$20,053/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$643万
+$19,128/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 301呎 (1房)
+$556万
+$18,456/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$589万
+$22,153/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$624万
+$19,638/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$843万
+$16,798/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$619万
+$17,842/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$540万
+$19,932/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$888万
+$17,485/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$860万
+$18,687/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$636万
+$18,938/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$503万
+$16,648/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$549万
+$20,644/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$657万
+$20,659/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 503呎 (2房)
+$877万
+$17,428/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$613万
+$17,665/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$535万
+$19,735/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$933万
+$18,359/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$913万
+$19,855/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$636万
+$18,938/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$502万
+$16,633/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$583万
+$21,934/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$657万
+$20,659/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$877万
+$17,463/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$644万
+$18,549/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$376万
+$13,888/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$914万
+$17,999/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$765万
+$16,633/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$624万
+$18,567/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 301呎 (1房)
+$566万
+$18,811/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$538万
+$20,239/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$644万
+$20,254/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$859万
+$17,120/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$551万
+$15,888/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$499万
+$18,427/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$862万
+$16,973/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$834万
+$18,139/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$539万
+$16,049/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$534万
+$17,679/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$533万
+$20,039/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$638万
+$20,053/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 503呎 (2房)
+$810万
+$16,112/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$595万
+$17,148/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$519万
+$19,156/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$745万
+$14,670/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 460呎 (2房)
+$826万
+$17,960/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$612万
+$18,201/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+$502万
+$16,621/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$561万
+$21,080/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 318呎 (1房)
+$594万
+$18,687/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$843万
+$16,783/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 347呎 (1房)
+$589万
+$16,978/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 271呎 (开放式)
+$514万
+$18,967/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1059万
+$21,800/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 436呎 (2房)
+$751万
+$17,233/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 313呎 (1房)
+$682万
+$21,800/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 275呎 (1房)
+$616万
+$22,400/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 240呎 (开放式)
+$562万
+$23,400/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 296呎 (1房)
+$663万
+$22,400/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$1000万
+$21,598/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>H | 324呎 (1房)
+$583万
+$18,007/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 247呎 (开放式)
+$592万
+$23,975/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1819呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+$875万
+$17,357/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1738万
+$21,784/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1286万
+$25,125/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$858万
+$17,067/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$876万
+$17,619/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$951万
+$17,716/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 516呎 (2房)
+$980万
+$19,001/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$808万
+$23,080/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$963万
+$21,160/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 2117呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+      <c r="K7" s="21" t="inlineStr"/>
+      <c r="L7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 799呎 (3房)
+$1704万
+$21,330/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1179万
+$23,026/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$860万
+$17,131/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$851万
+$17,129/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$925万
+$17,224/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1187万
+$22,830/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$818万
+$18,178/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$587万
+$24,762/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$671万
+$19,071/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$841万
+$24,042/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$981万
+$21,571/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1827万
+$22,901/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1232万
+$24,070/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$760万
+$15,117/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$845万
+$16,993/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1095万
+$21,065/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$970万
+$21,553/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$611万
+$25,794/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$783万
+$22,233/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$776万
+$22,184/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$962万
+$21,148/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1638万
+$20,527/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$870万
+$16,990/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$754万
+$14,998/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$838万
+$16,858/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$819万
+$15,257/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1074万
+$20,652/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$800万
+$17,773/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$564万
+$23,801/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$767万
+$21,797/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$761万
+$21,749/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$943万
+$20,734/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 799呎 (3房)
+$1703万
+$21,314/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$867万
+$16,939/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$1092万
+$21,762/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$828万
+$16,653/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$903万
+$16,817/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1130万
+$21,726/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$919万
+$20,423/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$691万
+$29,168/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$723万
+$20,553/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$801万
+$22,879/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$934万
+$20,529/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 799呎 (3房)
+$1606万
+$20,098/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1082万
+$21,132/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$847万
+$16,882/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$842万
+$16,913/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$806万
+$15,015/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1119万
+$21,511/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$910万
+$20,221/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$576万
+$24,307/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$752万
+$21,367/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$793万
+$22,653/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$881万
+$19,357/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 799呎 (3房)
+$1669万
+$20,894/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$864万
+$16,900/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$1071万
+$21,333/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$738万
+$14,844/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$889万
+$16,551/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1160万
+$22,300/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$789万
+$17,528/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$537万
+$22,650/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$709万
+$20,149/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$785万
+$22,429/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$872万
+$19,166/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1692万
+$21,206/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$862万
+$16,870/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$825万
+$16,397/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$736万
+$14,817/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$882万
+$16,420/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1032万
+$19,847/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$914万
+$20,306/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$565万
+$23,828/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$702万
+$19,949/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$777万
+$22,207/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$863万
+$18,976/呎
+(20年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1637万
+$20,508/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1146万
+$22,427/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$741万
+$14,731/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$735万
+$14,790/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$896万
+$16,684/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$929万
+$17,862/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$862万
+$19,147/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$559万
+$23,592/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$730万
+$20,739/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$770万
+$21,987/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$898万
+$19,727/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1620万
+$20,305/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1070万
+$20,940/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$1039万
+$20,706/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1039万
+$20,858/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1105万
+$20,570/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1012万
+$19,455/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$853万
+$18,958/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$554万
+$23,358/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$706万
+$20,045/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$717万
+$20,489/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$889万
+$19,532/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1601万
+$20,067/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1057万
+$20,643/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$1029万
+$20,501/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1142万
+$22,932/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1184万
+$22,044/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1064万
+$20,467/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$845万
+$18,770/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$645万
+$27,208/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$716万
+$20,330/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$754万
+$21,553/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$838万
+$18,418/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1525万
+$19,112/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$1057万
+$20,643/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$1057万
+$21,048/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$815万
+$16,365/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1150万
+$21,414/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$1096万
+$21,069/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$861万
+$19,131/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$645万
+$27,208/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$716万
+$20,330/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$754万
+$21,553/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$838万
+$18,418/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1570万
+$19,674/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$977万
+$19,088/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$954万
+$19,012/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$828万
+$16,633/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1011万
+$18,836/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$983万
+$18,903/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$833万
+$18,514/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$501万
+$21,132/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$660万
+$18,752/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$664万
+$18,959/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$775万
+$17,026/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 799呎 (3房)
+$1480万
+$18,528/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$840万
+$16,432/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$945万
+$18,786/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$977万
+$19,616/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1001万
+$18,649/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$973万
+$18,716/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$825万
+$18,331/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$527万
+$22,231/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$686万
+$19,495/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$690万
+$19,709/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$803万
+$17,650/呎
+(20年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1466万
+$18,368/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$958万
+$18,748/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$982万
+$19,569/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$967万
+$19,422/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$992万
+$18,465/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$918万
+$17,648/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$797万
+$17,717/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$522万
+$22,011/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$679万
+$19,302/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$683万
+$19,514/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$835万
+$18,349/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1524万
+$19,095/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$903万
+$17,679/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$926万
+$18,453/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+$958万
+$19,269/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$982万
+$18,282/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$909万
+$17,473/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$809万
+$17,969/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$486万
+$20,511/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$673万
+$19,111/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$644万
+$18,401/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$756万
+$16,622/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1437万
+$18,006/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$939万
+$18,343/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$963万
+$19,184/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$1007万
+$20,230/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1021万
+$19,006/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$666万
+$12,808/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$801万
+$17,792/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$511万
+$21,577/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$666万
+$18,921/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$670万
+$19,130/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$756万
+$16,622/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1423万
+$17,828/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$930万
+$18,162/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$953万
+$18,994/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$997万
+$20,029/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$935万
+$17,985/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$793万
+$17,615/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$477万
+$20,107/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$659万
+$18,734/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$663万
+$18,940/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$810万
+$17,809/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1479万
+$18,533/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$921万
+$17,982/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$736万
+$14,630/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$988万
+$19,831/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$882万
+$16,959/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$766万
+$17,026/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$472万
+$19,908/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$653万
+$18,549/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$656万
+$18,753/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$802万
+$17,633/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1409万
+$17,651/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$877万
+$17,125/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$944万
+$18,806/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$988万
+$19,831/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$953万
+$17,744/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$926万
+$17,807/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$785万
+$17,441/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$501万
+$21,152/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$653万
+$18,549/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$656万
+$18,753/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$802万
+$17,633/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1450万
+$18,170/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$711万
+$13,915/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$926万
+$18,437/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$968万
+$19,442/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$981万
+$18,266/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$835万
+$16,049/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$769万
+$17,099/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$491万
+$20,737/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$640万
+$18,185/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$613万
+$17,510/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$787万
+$17,287/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1436万
+$17,990/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$711万
+$13,915/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 503呎 (2房)
+$873万
+$17,351/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$902万
+$18,117/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$971万
+$18,085/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$899万
+$17,285/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$726万
+$16,124/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$458万
+$19,324/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$585万
+$16,633/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$637万
+$18,203/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$779万
+$17,116/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 798呎 (3房)
+$1582万
+$19,827/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$843万
+$16,459/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 502呎 (2房)
+$907万
+$18,074/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+$949万
+$19,059/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$962万
+$17,906/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 520呎 (2房)
+$848万
+$16,299/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$718万
+$15,964/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$453万
+$19,133/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 352呎 (1房)
+$628万
+$17,827/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>K | 350呎 (1房)
+$631万
+$18,023/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L29" s="22" t="inlineStr">
+        <is>
+          <t>L | 455呎 (2房)
+$771万
+$16,946/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 752呎 (3房)
+$1557万
+$20,700/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 472呎 (2房)
+$1031万
+$21,841/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1019万
+$22,000/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$1038万
+$21,853/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$1128万
+$21,899/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 498呎 (2房)
+$1081万
+$21,700/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>G | 428呎 (2房)
+$942万
+$22,000/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>H | 237呎 (开放式)
+$550万
+$23,200/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 329呎 (1房)
+$555万
+$16,867/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>K | 328呎 (1房)
+$739万
+$22,524/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>L | 433呎 (2房)
+$900万
+$20,785/呎
+(21年-01月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸.xlsx
@@ -665,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
